--- a/Statistics/400m Fri_statistics.xlsx
+++ b/Statistics/400m Fri_statistics.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G188"/>
+  <dimension ref="A1:G194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1241,12 +1241,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Thomas Johansen</t>
+          <t>Manith Randula Attanapola</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4.26,41</t>
+          <t>4.26,47</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>06.02.2015</t>
+          <t>08.02.2013</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1276,12 +1276,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Manith Randula Attanapola</t>
+          <t>Thomas Johansen</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4.26,47</t>
+          <t>4.26,41</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>08.02.2013</t>
+          <t>06.02.2015</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1556,25 +1556,25 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ole Peder Uthus Solum</t>
+          <t>Gabriel Rognes Steen</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4.30,99</t>
+          <t>4.33,98</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>29.09.2018</t>
+          <t>15.01.2023</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gabriel Rognes Steen</t>
+          <t>Ask Yifei Baldersheim</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4.33,98</t>
+          <t>4.34,05</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>15.01.2023</t>
+          <t>14.11.2021</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1626,25 +1626,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ask Yifei Baldersheim</t>
+          <t>Balder Baarholm</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4.34,05</t>
+          <t>4.35,07</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>14.11.2021</t>
+          <t>07.06.2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Porsgrunn</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1661,25 +1661,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Balder Baarholm</t>
+          <t>Miguel Marteira do Carvalho</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4.35,07</t>
+          <t>4.35,21</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>07.06.2025</t>
+          <t>09.04.2016</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Porsgrunn</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1696,25 +1696,25 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Miguel Marteira do Carvalho</t>
+          <t>Olav Nygård Bergum</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4.35,21</t>
+          <t>4.36,20</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>09.04.2016</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Arnt Martin Ystenes</t>
+          <t>Scott Rene Høgenhaug</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1814,12 +1814,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>22.01.2010</t>
+          <t>06.10.2017</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1836,7 +1836,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Scott Rene Høgenhaug</t>
+          <t>Arnt Martin Ystenes</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>06.10.2017</t>
+          <t>22.01.2010</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2011,12 +2011,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Vegard Skjervold</t>
+          <t>Aksel Viken Refseth</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4.39,45</t>
+          <t>4.39,38</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>18.01.2019</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2081,25 +2081,25 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Jenny Marandon Natvik</t>
+          <t>Vegard Skjervold</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5.04,87</t>
+          <t>4.39,45</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>18.10.2015</t>
+          <t>18.01.2019</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2116,25 +2116,25 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Erlend Søderlund</t>
+          <t>Jenny Marandon Natvik</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4.40,47</t>
+          <t>5.04,87</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>05.04.2013</t>
+          <t>18.10.2015</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Fauske</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2151,25 +2151,25 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Daniel Moen Manriquez</t>
+          <t>Erlend Søderlund</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4.40,61</t>
+          <t>4.40,47</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>09.02.2018</t>
+          <t>05.04.2013</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Fauske</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2186,25 +2186,25 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Vårin Berge Jensås</t>
+          <t>Daniel Moen Manriquez</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5.06,75</t>
+          <t>4.40,61</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>15.03.2019</t>
+          <t>09.02.2018</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2221,25 +2221,25 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Joakim Gjerde</t>
+          <t>Vårin Berge Jensås</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>4.42,65</t>
+          <t>5.06,75</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>16.01.2015</t>
+          <t>15.03.2019</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2256,20 +2256,20 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Andreas Aglen Alsos</t>
+          <t>Joakim Gjerde</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4.42,86</t>
+          <t>4.42,65</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>17.03.2023</t>
+          <t>16.01.2015</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2291,12 +2291,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Inger Lise Wolf</t>
+          <t>Andreas Aglen Alsos</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5.08,23</t>
+          <t>4.42,86</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>17.01.2020</t>
+          <t>17.03.2023</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2326,20 +2326,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ole Andreas Alsos</t>
+          <t>Inger Lise Wolf</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>4.43,44</t>
+          <t>5.08,23</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>09.04.2016</t>
+          <t>17.01.2020</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2361,20 +2361,20 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Henning Andersson</t>
+          <t>Ole Andreas Alsos</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>4.43,75</t>
+          <t>4.43,44</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>17.01.2014</t>
+          <t>09.04.2016</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2396,25 +2396,25 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Tobias Gilbu</t>
+          <t>Henning Andersson</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>4.44,37</t>
+          <t>4.43,75</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>01.12.2018</t>
+          <t>17.01.2014</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2431,25 +2431,25 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sander Haugan</t>
+          <t>Tobias Gilbu</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>4.45,73</t>
+          <t>4.44,37</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>30.11.2019</t>
+          <t>01.12.2018</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2466,20 +2466,20 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Alfred Fenstad Høysæter</t>
+          <t>Emmelin Munkhaugen</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4.46,05</t>
+          <t>5.09,95</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>17.04.2021</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2501,25 +2501,25 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Thais Farias Kristiansen</t>
+          <t>Lucas Nachappa Muthanna</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5.12,87</t>
+          <t>4.45,84</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>15.03.2019</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2536,25 +2536,25 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ådne Viken Refseth</t>
+          <t>Sander Haugan</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>4.47,47</t>
+          <t>4.45,73</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>17.01.2016</t>
+          <t>30.11.2019</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2571,25 +2571,25 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Emmelin Munkhaugen</t>
+          <t>Alfred Fenstad Høysæter</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5.13,66</t>
+          <t>4.46,05</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>07.06.2025</t>
+          <t>17.04.2021</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Porsgrunn</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2606,25 +2606,25 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sondre Furmyr Johansen</t>
+          <t>Thais Farias Kristiansen</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>4.48,17</t>
+          <t>5.12,87</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>03.12.2022</t>
+          <t>15.03.2019</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2641,25 +2641,25 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Elian Theodor Kringstad</t>
+          <t>Ådne Viken Refseth</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4.50,10</t>
+          <t>4.47,47</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>15.03.2024</t>
+          <t>17.01.2016</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2676,25 +2676,25 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Aksel Viken Refseth</t>
+          <t>Sondre Furmyr Johansen</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>4.50,39</t>
+          <t>4.48,17</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>17.01.2025</t>
+          <t>03.12.2022</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2711,25 +2711,25 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Olav Nygård Bergum</t>
+          <t>Elian Theodor Kringstad</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4.50,29</t>
+          <t>4.50,10</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>17.01.2025</t>
+          <t>15.03.2024</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2781,25 +2781,25 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Hans Ourson Liem</t>
+          <t>Bjørn Eimar Endal Sorteberg</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>4.52,01</t>
+          <t>4.51,70</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>18.03.2022</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Orkanger</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2816,25 +2816,25 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Even Kristoffer Lind Bøckman</t>
+          <t>Hans Ourson Liem</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>4.52,46</t>
+          <t>4.52,01</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>17.01.2020</t>
+          <t>18.03.2022</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Orkanger</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2851,20 +2851,20 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Carl Victor Mukisa Nygård</t>
+          <t>Even Kristoffer Lind Bøckman</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>4.54,06</t>
+          <t>4.52,46</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>17.03.2023</t>
+          <t>17.01.2020</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2886,20 +2886,20 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Einar Woldseth</t>
+          <t>Vishnu Sattanathan</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>4.54,20</t>
+          <t>4.53,18</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>17.01.2025</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2921,25 +2921,25 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Hasith Ransiri Attanapola</t>
+          <t>Carl Victor Mukisa Nygård</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>4.54,19</t>
+          <t>4.54,06</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>15.03.2019</t>
+          <t>17.03.2023</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2956,25 +2956,25 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Vishnu Sattanathan</t>
+          <t>Einar Woldseth</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>4.54,99</t>
+          <t>4.54,20</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>17.01.2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2991,25 +2991,25 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Tamer Saleh Abuzid</t>
+          <t>Hasith Ransiri Attanapola</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>4.57,12</t>
+          <t>4.54,19</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>20.09.2020</t>
+          <t>15.03.2019</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3026,25 +3026,25 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Kjersti Skauge Bysting</t>
+          <t>Ludvig Svendsen</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5.25,48</t>
+          <t>4.56,84</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>14.01.2006</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3061,20 +3061,20 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Edvin Aurstad Bergum</t>
+          <t>Tamer Saleh Abuzid</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>4.59,54</t>
+          <t>4.57,12</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>17.01.2025</t>
+          <t>20.09.2020</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3096,20 +3096,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Erin Elizabeth Bachynski</t>
+          <t>Kjersti Skauge Bysting</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5.27,81</t>
+          <t>5.25,48</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>09.04.2016</t>
+          <t>14.01.2006</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3131,25 +3131,25 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Bjørn Eimar Endal Sorteberg</t>
+          <t>Edvin Aurstad Bergum</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5.04,75</t>
+          <t>4.59,54</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>17.01.2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3166,20 +3166,20 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Iris Elise Moen</t>
+          <t>Erin Elizabeth Bachynski</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5.32,56</t>
+          <t>5.27,81</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>17.04.2021</t>
+          <t>09.04.2016</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3236,12 +3236,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Lucas Nachappa Muthanna</t>
+          <t>Iris Elise Moen</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5.05,05</t>
+          <t>5.32,56</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>16.02.2025</t>
+          <t>17.04.2021</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3306,12 +3306,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Ludvig Svendsen</t>
+          <t>Eilert Juul Wolfgang</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5.08,36</t>
+          <t>5.08,30</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>09.02.2013</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3341,25 +3341,25 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Eilert Juul Wolfgang</t>
+          <t>Lin Carola Magdalene Nygren</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5.08,30</t>
+          <t>5.34,58</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>09.02.2013</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3376,25 +3376,25 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Kristin Myhr Pettersen</t>
+          <t>Edvard Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5.37,02</t>
+          <t>5.08,97</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>26.10.2013</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3411,25 +3411,25 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Daniel Haugen Ngwenya</t>
+          <t>Kristin Myhr Pettersen</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5.09,59</t>
+          <t>5.37,02</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>08.03.2008</t>
+          <t>26.10.2013</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3446,25 +3446,25 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Tony Christopher Moflag</t>
+          <t>Daniel Haugen Ngwenya</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5.10,69</t>
+          <t>5.09,59</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>07.10.2006</t>
+          <t>08.03.2008</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3481,25 +3481,25 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Håkon Johansen</t>
+          <t>Mattias Isaksen</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5.11,84</t>
+          <t>5.10,45</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>25.03.2006</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3516,25 +3516,25 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Simon Perssønn Mørseth</t>
+          <t>Tony Christopher Moflag</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5.12,79</t>
+          <t>5.10,69</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>15.03.2024</t>
+          <t>07.10.2006</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3551,25 +3551,25 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Theodor Solheim</t>
+          <t>Edvin Grenne Spangelo</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5.12,76</t>
+          <t>5.11,38</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>25.10.2020</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3586,25 +3586,25 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Leo Petter Hauge Sølvberg</t>
+          <t>Håkon Johansen</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5.16,28</t>
+          <t>5.11,84</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>05.02.2016</t>
+          <t>25.03.2006</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3621,16 +3621,16 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Lionel Nicolas Weissbrodt</t>
+          <t>Simon Perssønn Mørseth</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5.17,01</t>
+          <t>5.12,79</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -3656,25 +3656,25 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Storm Olander Øvergård</t>
+          <t>Theodor Solheim</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5.18,05</t>
+          <t>5.12,76</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>25.10.2020</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3691,25 +3691,25 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Dhanushi Attanapola</t>
+          <t>Leo Petter Hauge Sølvberg</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5.46,80</t>
+          <t>5.16,28</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>22.05.2009</t>
+          <t>05.02.2016</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3726,25 +3726,25 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Geir Atle Hoff</t>
+          <t>Daniel Stanislaw Czuba</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5.20,76</t>
+          <t>5.16,52</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>13.03.2010</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3761,25 +3761,25 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Edvard Hamnes Ulriksen</t>
+          <t>Lionel Nicolas Weissbrodt</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5.20,94</t>
+          <t>5.17,01</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>07.06.2025</t>
+          <t>15.03.2024</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Porsgrunn</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3796,25 +3796,25 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sondre Grimsmo</t>
+          <t>Storm Olander Øvergård</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5.22,07</t>
+          <t>5.18,05</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>10.02.2008</t>
+          <t>14.03.2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3831,25 +3831,25 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Daniel Stanislaw Czuba</t>
+          <t>Dhanushi Attanapola</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5.21,78</t>
+          <t>5.46,80</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>17.01.2025</t>
+          <t>22.05.2009</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3866,25 +3866,25 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Gunnleif Nielsen</t>
+          <t>Geir Atle Hoff</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5.23,55</t>
+          <t>5.20,76</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>09.03.2019</t>
+          <t>13.03.2010</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3901,25 +3901,25 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Vegard Maaø</t>
+          <t>Eirik Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5.23,76</t>
+          <t>5.20,93</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>21.03.2010</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3936,25 +3936,25 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Jonas D. Lesund</t>
+          <t>Sondre Grimsmo</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5.24,44</t>
+          <t>5.22,07</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>05.04.2014</t>
+          <t>10.02.2008</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3971,20 +3971,20 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sondre Aakerholm Adsen</t>
+          <t>Philip Giske Nyman</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5.25,02</t>
+          <t>5.22,44</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>26.01.2024</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4006,25 +4006,25 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ingjerd Jepsen Vegge</t>
+          <t>Gunnleif Nielsen</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5.54,12</t>
+          <t>5.23,55</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>12.03.2011</t>
+          <t>09.03.2019</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4041,25 +4041,25 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Eirik Ingeberg Garshol</t>
+          <t>Vegard Maaø</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5.27,46</t>
+          <t>5.23,76</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>21.03.2010</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4076,25 +4076,25 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Johan Mostervik</t>
+          <t>Jonas D. Lesund</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5.27,44</t>
+          <t>5.24,44</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>09.02.2018</t>
+          <t>05.04.2014</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4111,25 +4111,25 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Thomas Stur Ekrem</t>
+          <t>Sondre Aakerholm Adsen</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5.27,70</t>
+          <t>5.25,02</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>22.10.2023</t>
+          <t>26.01.2024</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4146,25 +4146,25 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Edvin Grenne Spangelo</t>
+          <t>Ingjerd Jepsen Vegge</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5.28,27</t>
+          <t>5.54,12</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>12.03.2011</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4181,25 +4181,25 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Mattias Isaksen</t>
+          <t>Ellen Kristine Eidsmo Hova</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5.28,44</t>
+          <t>5.53,89</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>10.02.2024</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4216,25 +4216,25 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Magnus Svindland Næsgaard</t>
+          <t>Johan Mostervik</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5.28,83</t>
+          <t>5.27,44</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>04.12.2021</t>
+          <t>09.02.2018</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4251,25 +4251,25 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Wiggo Røst</t>
+          <t>Eirik Ingeberg Garshol</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5.29,58</t>
+          <t>5.27,46</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>13.03.2009</t>
+          <t>14.03.2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kirkenes</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4286,25 +4286,25 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>David Csejtey</t>
+          <t>Thomas Stur Ekrem</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5.29,28</t>
+          <t>5.27,70</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>17.04.2021</t>
+          <t>22.10.2023</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kolvereid</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4321,25 +4321,25 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Pedro Manquehual</t>
+          <t>Fredrik Holberg</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5.30,40</t>
+          <t>5.27,74</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4356,25 +4356,25 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Christian Bauer</t>
+          <t>Magnus Svindland Næsgaard</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5.31,18</t>
+          <t>5.28,83</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>01.04.2011</t>
+          <t>04.12.2021</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4391,25 +4391,25 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Brage Gylseth Dahl</t>
+          <t>David Csejtey</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5.32,68</t>
+          <t>5.29,28</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>17.04.2021</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4426,25 +4426,25 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Lyder Ringsvold Hogstad</t>
+          <t>Wiggo Røst</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5.33,47</t>
+          <t>5.29,58</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>15.03.2019</t>
+          <t>13.03.2009</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Kirkenes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4461,25 +4461,25 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Christian Dahle-Øfsti</t>
+          <t>Pedro Manquehual</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5.34,19</t>
+          <t>5.30,40</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>05.10.2013</t>
+          <t>14.03.2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4496,25 +4496,25 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Eirik Hamnes Ulriksen</t>
+          <t>Brage Gylseth Dahl</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5.34,70</t>
+          <t>5.30,65</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4531,25 +4531,25 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Vegard S. Wigum</t>
+          <t>Christian Bauer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5.34,54</t>
+          <t>5.31,18</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>05.04.2014</t>
+          <t>01.04.2011</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4566,25 +4566,25 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Leander Gisvold Restad</t>
+          <t>Lyder Ringsvold Hogstad</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5.35,59</t>
+          <t>5.33,47</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>30.11.2019</t>
+          <t>15.03.2019</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4601,25 +4601,25 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Bjarne Forfot</t>
+          <t>Christian Dahle-Øfsti</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5.37,58</t>
+          <t>5.34,19</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>03.12.2016</t>
+          <t>05.10.2013</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4636,25 +4636,25 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ivan Erikovitch Alvestad</t>
+          <t>Vegard S. Wigum</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5.37,91</t>
+          <t>5.34,54</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>17.04.2021</t>
+          <t>05.04.2014</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4671,25 +4671,25 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Lin Carola Magdalene Nygren</t>
+          <t>Leander Gisvold Restad</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>6.08,30</t>
+          <t>5.35,59</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>30.11.2019</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4706,25 +4706,25 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Njål Høie</t>
+          <t>Bjarne Forfot</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5.37,83</t>
+          <t>5.37,58</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>07.12.2013</t>
+          <t>03.12.2016</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Volda</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4741,25 +4741,25 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Paal Aagaard</t>
+          <t>Ivan Erikovitch Alvestad</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5.41,86</t>
+          <t>5.37,91</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>13.03.2010</t>
+          <t>17.04.2021</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4776,25 +4776,25 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Fredrik Holberg</t>
+          <t>Njål Høie</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5.43,79</t>
+          <t>5.37,83</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>07.12.2013</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Volda</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4811,25 +4811,25 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ellen Kristine Eidsmo Hova</t>
+          <t>Paal Aagaard</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>6.16,49</t>
+          <t>5.41,86</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>13.03.2010</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4881,12 +4881,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Ailin Østerås</t>
+          <t>Olav Høyland Hofstad</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>6.19,89</t>
+          <t>5.48,78</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>18.06.2011</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4916,25 +4916,25 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Jon Noé Høye</t>
+          <t>Ailin Østerås</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5.49,92</t>
+          <t>6.19,89</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>29.09.2019</t>
+          <t>18.06.2011</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4951,25 +4951,25 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Anton Sergeevich Gorodkov</t>
+          <t>Jon Noé Høye</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5.53,10</t>
+          <t>5.49,92</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>06.02.2015</t>
+          <t>29.09.2019</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4986,20 +4986,20 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Philip Giske Nyman</t>
+          <t>Anton Sergeevich Gorodkov</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5.55,79</t>
+          <t>5.53,10</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>06.02.2015</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5021,25 +5021,25 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Magnus Bakkejord</t>
+          <t>Liv Løfaldli</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5.56,48</t>
+          <t>6.25,67</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>15.10.2011</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Brunflo</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5056,12 +5056,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Isabel Ødegård Pedersen</t>
+          <t>Magnus Bakkejord</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>6.27,94</t>
+          <t>5.56,48</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>22.02.2025</t>
+          <t>15.10.2011</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Brunflo</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5091,25 +5091,25 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Victor Voormolen Gutierrez</t>
+          <t>Isabel Ødegård Pedersen</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5.58,79</t>
+          <t>6.27,94</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>16.02.2019</t>
+          <t>22.02.2025</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5126,25 +5126,25 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Kaan Baltaci</t>
+          <t>Gunhild Furuholt Valle</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>6.00,75</t>
+          <t>6.27,78</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>03.12.2022</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5161,25 +5161,25 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Oscar Kvaløy Tiller</t>
+          <t>Victor Voormolen Gutierrez</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>6.02,45</t>
+          <t>5.58,79</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>20.09.2020</t>
+          <t>16.02.2019</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5196,25 +5196,25 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Anton Hoel</t>
+          <t>Kaan Baltaci</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>6.06,85</t>
+          <t>6.00,75</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>15.09.2013</t>
+          <t>03.12.2022</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5231,25 +5231,25 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Morten Schanke</t>
+          <t>Ingeborg Strandenes</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>6.08,40</t>
+          <t>6.31,25</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>08.04.2016</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5266,25 +5266,25 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Peder Lund Juul</t>
+          <t>Cornelius Wik</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>6.09,76</t>
+          <t>6.01,69</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>06.04.2024</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5301,20 +5301,20 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Håkon Emil Øien</t>
+          <t>Sigurd Øie Seland</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>6.14,37</t>
+          <t>6.02,07</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>15.06.2013</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5336,20 +5336,20 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Jakob M. Tjøstheim</t>
+          <t>Oscar Kvaløy Tiller</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>6.15,41</t>
+          <t>6.02,45</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>21.06.2014</t>
+          <t>20.09.2020</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5371,25 +5371,25 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Thomas Paulsen</t>
+          <t>Ruolai Liu</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>6.16,34</t>
+          <t>6.38,30</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>08.02.2014</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5406,25 +5406,25 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Liv Løfaldli</t>
+          <t>Anton Hoel</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>6.51,60</t>
+          <t>6.06,85</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>16.02.2025</t>
+          <t>15.09.2013</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5441,20 +5441,20 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Emily Liv Liem</t>
+          <t>Morten Schanke</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>6.53,66</t>
+          <t>6.08,40</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>18.01.2019</t>
+          <t>08.04.2016</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5476,25 +5476,25 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Ingeborg Strandenes</t>
+          <t>Peder Lund Juul</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>7.00,04</t>
+          <t>6.09,76</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>06.04.2024</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5511,25 +5511,25 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>William Johannes Kirkelund Kristiansen</t>
+          <t>Jesper Julius Sundseth Skjærli</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>6.30,82</t>
+          <t>6.11,36</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>19.03.2022</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Orkanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5546,25 +5546,25 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Sigurd Øie Seland</t>
+          <t>Rasmus Larsen Natvig</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>6.32,26</t>
+          <t>6.12,30</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>08.12.2024</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5581,25 +5581,25 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>William Wale</t>
+          <t>Bernard Smuk</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>6.34,36</t>
+          <t>6.14,00</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>21.06.2014</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5616,25 +5616,25 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Tymofii Dzisiak</t>
+          <t>Håkon Emil Øien</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>6.36,67</t>
+          <t>6.14,37</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>16.02.2025</t>
+          <t>15.06.2013</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5651,25 +5651,25 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Rasmus Larsen Natvig</t>
+          <t>Jakob M. Tjøstheim</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>6.37,26</t>
+          <t>6.15,41</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>16.02.2025</t>
+          <t>21.06.2014</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5686,25 +5686,25 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Marit Søberg</t>
+          <t>Thomas Paulsen</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>7.14,27</t>
+          <t>6.16,34</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>20.09.2009</t>
+          <t>08.02.2014</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5721,20 +5721,20 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Sondre Thorgaard</t>
+          <t>Emily Liv Liem</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>6.38,53</t>
+          <t>6.53,66</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>17.04.2021</t>
+          <t>18.01.2019</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5756,25 +5756,25 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Einar Risholt Moen</t>
+          <t>William Johannes Kirkelund Kristiansen</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>6.39,20</t>
+          <t>6.30,82</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>20.04.2013</t>
+          <t>19.03.2022</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Orkanger</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5791,25 +5791,25 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Bernard Smuk</t>
+          <t>William Wale</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>6.40,79</t>
+          <t>6.34,36</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>21.06.2014</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5826,25 +5826,25 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Robin von Bargen</t>
+          <t>Tymofii Dzisiak</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>6.42,14</t>
+          <t>6.35,74</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>22.05.2009</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5861,25 +5861,25 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Olav Høyland Hofstad</t>
+          <t>Marit Søberg</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>6.43,02</t>
+          <t>7.14,27</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>20.09.2009</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5896,25 +5896,25 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Jesper Julius Sundseth Skjærli</t>
+          <t>Sondre Thorgaard</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>6.45,52</t>
+          <t>6.38,53</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>17.04.2021</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5931,20 +5931,20 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Gunhild Furuholt Valle</t>
+          <t>Erik Solbakken Andersen</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>7.23,93</t>
+          <t>6.38,29</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>30.11.2024</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5966,25 +5966,25 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Fredrik Hårsaker Myrenget</t>
+          <t>Einar Risholt Moen</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>6.49,43</t>
+          <t>6.39,20</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>19.01.2018</t>
+          <t>20.04.2013</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -6001,25 +6001,25 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Cornelius Wik</t>
+          <t>Robin von Bargen</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>6.51,12</t>
+          <t>6.42,14</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>08.12.2024</t>
+          <t>22.05.2009</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6036,25 +6036,25 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Kolbjørn Renhult Skaug</t>
+          <t>Ingeborg Vold Kirkvold</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>6.54,05</t>
+          <t>7.17,04</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>25.10.2014</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6071,20 +6071,20 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Marcus Thalberg Fagerheim</t>
+          <t>Mikkel Fenstad</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>6.54,27</t>
+          <t>6.44,88</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>18.09.2011</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -6106,25 +6106,25 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Erik Solbakken Andersen</t>
+          <t>Torben Bräuer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>6.56,50</t>
+          <t>6.46,19</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>17.01.2025</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6141,20 +6141,20 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Leo Alexander Farias Kristiansen</t>
+          <t>Fredrik Hårsaker Myrenget</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>6.57,95</t>
+          <t>6.49,43</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>20.09.2020</t>
+          <t>19.01.2018</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -6176,20 +6176,20 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Morten Johansen</t>
+          <t>Marcus Thalberg Fagerheim</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>7.04,68</t>
+          <t>6.54,27</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>14.01.2006</t>
+          <t>18.09.2011</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -6211,25 +6211,25 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Magnus Hestvik Larsen</t>
+          <t>Kolbjørn Renhult Skaug</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>7.07,68</t>
+          <t>6.54,05</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>14.02.2009</t>
+          <t>25.10.2014</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6246,25 +6246,25 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Vår Kristine Sollien Skar</t>
+          <t>Lilly Fludal Osland</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>7.57,14</t>
+          <t>7.31,16</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>08.02.2014</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6281,20 +6281,20 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Arild Håkonsen Stixrud</t>
+          <t>Leo Alexander Farias Kristiansen</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>7.20,26</t>
+          <t>6.57,95</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>08.12.2024</t>
+          <t>20.09.2020</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -6316,20 +6316,20 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Ingvar Høgås Wik</t>
+          <t>Morten Johansen</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>7.23,47</t>
+          <t>7.04,68</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>09.02.2013</t>
+          <t>14.01.2006</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -6351,25 +6351,25 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Ingeborg Vold Kirkvold</t>
+          <t>Magnus Hestvik Larsen</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>8.04,68</t>
+          <t>7.07,68</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>30.11.2024</t>
+          <t>14.02.2009</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6386,25 +6386,25 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Setareh Kulsum Sigrid Feyzi</t>
+          <t>Vår Kristine Sollien Skar</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>8.04,33</t>
+          <t>7.57,14</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>29.09.2018</t>
+          <t>08.02.2014</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6421,25 +6421,25 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Jesper Øvermo Johansen</t>
+          <t>Arild Håkonsen Stixrud</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>7.25,80</t>
+          <t>7.20,26</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>25.10.2020</t>
+          <t>08.12.2024</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6456,25 +6456,25 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Hauk Vold Kirkvold</t>
+          <t>Emil Falkenbo-Skalmerås</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>7.26,48</t>
+          <t>7.22,00</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>27.02.2022</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6491,20 +6491,20 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Vegard Olsvold</t>
+          <t>Ingvar Høgås Wik</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>7.35,09</t>
+          <t>7.23,47</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>17.01.2020</t>
+          <t>09.02.2013</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -6526,25 +6526,25 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Eirik Solligård</t>
+          <t>Setareh Kulsum Sigrid Feyzi</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>7.36,98</t>
+          <t>8.04,33</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>28.02.2009</t>
+          <t>29.09.2018</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6561,25 +6561,25 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Hans Otto Søyseth</t>
+          <t>Jesper Øvermo Johansen</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>7.41,13</t>
+          <t>7.25,80</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>29.11.2014</t>
+          <t>25.10.2020</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6596,25 +6596,25 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Filip Dalsaune</t>
+          <t>Hauk Vold Kirkvold</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>7.41,74</t>
+          <t>7.26,48</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>17.01.2025</t>
+          <t>27.02.2022</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6631,20 +6631,20 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Dominic Olav Sollien-Pearn</t>
+          <t>Vegard Olsvold</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>7.48,33</t>
+          <t>7.35,09</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>20.06.2021</t>
+          <t>17.01.2020</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -6666,25 +6666,25 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Sigurd Kristoffersen Torvik</t>
+          <t>Eirik Solligård</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>7.49,19</t>
+          <t>7.36,98</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>26.01.2024</t>
+          <t>28.02.2009</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6701,20 +6701,20 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>André Prestmo-Edvardsen</t>
+          <t>Filip Dalsaune</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>7.53,10</t>
+          <t>7.41,74</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>20.09.2020</t>
+          <t>17.01.2025</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -6736,25 +6736,25 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Nikan Ommani</t>
+          <t>Hans Otto Søyseth</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>7.56,73</t>
+          <t>7.41,13</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>08.12.2024</t>
+          <t>29.11.2014</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6771,25 +6771,25 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Ingolf Nicholay Stenskrog</t>
+          <t>Guy Løfaldli</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>7.59,84</t>
+          <t>7.41,81</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>07.12.2012</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6806,20 +6806,20 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Guangzhi Ma</t>
+          <t>Dominic Olav Sollien-Pearn</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>8.03,69</t>
+          <t>7.48,33</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>20.05.2006</t>
+          <t>20.06.2021</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -6841,25 +6841,25 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Nataniel Skjøndal-Bar</t>
+          <t>Sigurd Kristoffersen Torvik</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>8.04,47</t>
+          <t>7.49,19</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>20.10.2019</t>
+          <t>26.01.2024</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6876,20 +6876,20 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Gajithsing Ajeethsing</t>
+          <t>André Prestmo-Edvardsen</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>8.21,75</t>
+          <t>7.53,10</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>17.04.2021</t>
+          <t>20.09.2020</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6911,25 +6911,25 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Theodor Hoff</t>
+          <t>Nikan Ommani</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>8.23,55</t>
+          <t>7.56,73</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>20.04.2013</t>
+          <t>08.12.2024</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6946,25 +6946,25 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Casper Dahle-Øfsti</t>
+          <t>Ingolf Nicholay Stenskrog</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>8.28,80</t>
+          <t>7.59,84</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>20.10.2013</t>
+          <t>07.12.2012</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6981,33 +6981,243 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
+          <t>Guangzhi Ma</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>8.03,69</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>84</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>20.05.2006</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Nataniel Skjøndal-Bar</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>8.04,47</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>84</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>20.10.2019</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Verdal</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Gajithsing Ajeethsing</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>8.21,75</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>75</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>17.04.2021</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Noah Kvam Haaheim</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>8.22,42</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>75</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>19.10.2025</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Verdal</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Theodor Hoff</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>8.23,55</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>74</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>20.04.2013</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Stjørdal</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Casper Dahle-Øfsti</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>8.28,80</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>72</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>20.10.2013</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
           <t>Riccardo Manum</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
+      <c r="B194" t="inlineStr">
         <is>
           <t>8.51,65</t>
         </is>
       </c>
-      <c r="C188" t="n">
+      <c r="C194" t="n">
         <v>63</v>
       </c>
-      <c r="D188" t="inlineStr">
+      <c r="D194" t="inlineStr">
         <is>
           <t>17.01.2025</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Trondheim</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -8257,12 +8467,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Stian Nilsen</t>
+          <t>Emmelin Munkhaugen</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4.58,29</t>
+          <t>5.19,15</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -8270,12 +8480,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>24.04.2010</t>
+          <t>27.06.2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -8292,12 +8502,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Emmelin Munkhaugen</t>
+          <t>Stian Nilsen</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5.19,15</t>
+          <t>4.58,29</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -8305,12 +8515,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>27.06.2025</t>
+          <t>24.04.2010</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -8887,12 +9097,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bjarne Forfot</t>
+          <t>Eilert Juul Wolfgang</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5.31,37</t>
+          <t>5.31,63</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -8900,7 +9110,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>10.06.2017</t>
+          <t>14.06.2014</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -8922,12 +9132,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Eilert Juul Wolfgang</t>
+          <t>Bjarne Forfot</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5.31,63</t>
+          <t>5.31,37</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -8935,7 +9145,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>14.06.2014</t>
+          <t>10.06.2017</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -9097,7 +9307,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Tamer Saleh Abuzid</t>
+          <t>Daniel Stanislaw Czuba</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -9110,7 +9320,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>28.06.2019</t>
+          <t>28.06.2024</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -9132,7 +9342,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Daniel Stanislaw Czuba</t>
+          <t>Tamer Saleh Abuzid</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -9145,7 +9355,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>28.06.2024</t>
+          <t>28.06.2019</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -9910,7 +10120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G175"/>
+  <dimension ref="A1:G181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11318,25 +11528,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Rebekka Wangberg</t>
+          <t>Ada Fludal Osland</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5.04,39</t>
+          <t>5.02,24</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10.02.2017</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -11353,25 +11563,25 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Thora Bjarnøe Brandsegg</t>
+          <t>Rebekka Wangberg</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5.05,47</t>
+          <t>5.04,39</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>17.01.2025</t>
+          <t>10.02.2017</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -11388,25 +11598,25 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Marthe Kalvik</t>
+          <t>Thora Bjarnøe Brandsegg</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5.06,28</t>
+          <t>5.05,47</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>24.03.2007</t>
+          <t>17.01.2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -11423,25 +11633,25 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Marthe Eline Waagø-Hansen</t>
+          <t>Marthe Kalvik</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5.07,44</t>
+          <t>5.06,28</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>07.10.2006</t>
+          <t>24.03.2007</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -11458,25 +11668,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Thea Lervold Høffler</t>
+          <t>Marthe Eline Waagø-Hansen</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5.09,26</t>
+          <t>5.07,44</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>09.04.2016</t>
+          <t>07.10.2006</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -11493,25 +11703,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Gudrun Berg Ildstad</t>
+          <t>Thea Lervold Høffler</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5.09,44</t>
+          <t>5.09,26</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>21.05.2005</t>
+          <t>09.04.2016</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -11528,12 +11738,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Helle Krogstad</t>
+          <t>Gudrun Berg Ildstad</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5.09,53</t>
+          <t>5.09,44</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -11541,12 +11751,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10.02.2008</t>
+          <t>21.05.2005</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -11563,25 +11773,25 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Lisa Ling Klauseth Liasjø</t>
+          <t>Helle Krogstad</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5.09,70</t>
+          <t>5.09,53</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>30.11.2019</t>
+          <t>10.02.2008</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -11598,25 +11808,25 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ada Viken Refseth</t>
+          <t>Lisa Ling Klauseth Liasjø</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5.10,56</t>
+          <t>5.09,70</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>26.10.2019</t>
+          <t>30.11.2019</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -11633,25 +11843,25 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Hedda Østgaard</t>
+          <t>Ada Viken Refseth</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5.10,70</t>
+          <t>5.10,56</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>08.05.2010</t>
+          <t>26.10.2019</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -11738,25 +11948,25 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Camilla Dahle-Øfsti</t>
+          <t>Hedda Østgaard</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5.11,11</t>
+          <t>5.10,70</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>06.02.2015</t>
+          <t>08.05.2010</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -11773,25 +11983,25 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Oda Sem Austmo</t>
+          <t>Sissel Furuholt Valle</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5.12,84</t>
+          <t>5.09,36</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>11.05.2013</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -11808,25 +12018,25 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Elisaveta Røste</t>
+          <t>Camilla Dahle-Øfsti</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5.13,54</t>
+          <t>5.11,11</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>20.09.2020</t>
+          <t>06.02.2015</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -11843,20 +12053,20 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Vilde Austmo</t>
+          <t>Alexandra Contreras Jimenez</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5.13,52</t>
+          <t>5.11,42</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>09.02.2018</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -11878,25 +12088,25 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Thea Haugan</t>
+          <t>Oda Sem Austmo</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5.13,82</t>
+          <t>5.12,84</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>30.11.2019</t>
+          <t>11.05.2013</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11913,20 +12123,20 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Elise Nygård</t>
+          <t>Elisaveta Røste</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5.14,45</t>
+          <t>5.13,54</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>11.02.2011</t>
+          <t>20.09.2020</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -11948,25 +12158,25 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Annika Krill</t>
+          <t>Vilde Austmo</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5.14,45</t>
+          <t>5.13,52</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>12.03.2005</t>
+          <t>09.02.2018</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11983,25 +12193,25 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Kristina Elena Bjørklund Mora</t>
+          <t>Thea Haugan</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5.14,56</t>
+          <t>5.13,82</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>08.02.2013</t>
+          <t>30.11.2019</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -12018,20 +12228,20 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Erika Nicole Hagen</t>
+          <t>Elise Nygård</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5.14,90</t>
+          <t>5.14,45</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>14.11.2021</t>
+          <t>11.02.2011</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -12053,25 +12263,25 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Heidi Elisabeth Ysland</t>
+          <t>Annika Krill</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5.15,26</t>
+          <t>5.14,45</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10.02.2017</t>
+          <t>12.03.2005</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12088,20 +12298,20 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Maja Graczyk</t>
+          <t>Kristina Elena Bjørklund Mora</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5.15,56</t>
+          <t>5.14,56</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>09.02.2018</t>
+          <t>08.02.2013</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -12123,20 +12333,20 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Monica Wold Gustafson</t>
+          <t>Erika Nicole Hagen</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5.17,02</t>
+          <t>5.14,90</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>09.04.2016</t>
+          <t>14.11.2021</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -12158,20 +12368,20 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sissel Furuholt Valle</t>
+          <t>Heidi Elisabeth Ysland</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5.17,17</t>
+          <t>5.15,26</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>10.02.2017</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -12193,25 +12403,25 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Carina Aadahl</t>
+          <t>Maja Graczyk</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5.17,28</t>
+          <t>5.15,56</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>06.02.2015</t>
+          <t>09.02.2018</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12228,25 +12438,25 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Olea Winnberg</t>
+          <t>Monica Wold Gustafson</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5.17,41</t>
+          <t>5.17,02</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>15.03.2024</t>
+          <t>09.04.2016</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12263,25 +12473,25 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Miriam Vedvik</t>
+          <t>Carina Aadahl</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5.17,93</t>
+          <t>5.17,28</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>25.01.2008</t>
+          <t>06.02.2015</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -12298,25 +12508,25 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ada Fludal Osland</t>
+          <t>Olea Winnberg</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5.18,44</t>
+          <t>5.17,41</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>07.06.2025</t>
+          <t>15.03.2024</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Porsgrunn</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -12333,25 +12543,25 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Julie Mathilde Bjordal</t>
+          <t>Miriam Vedvik</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5.18,27</t>
+          <t>5.17,93</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10.02.2017</t>
+          <t>25.01.2008</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -12368,25 +12578,25 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Diana Stafsnes Califano</t>
+          <t>Julie Mathilde Bjordal</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5.19,87</t>
+          <t>5.18,27</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>19.10.2019</t>
+          <t>10.02.2017</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -12403,25 +12613,25 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Isabella Johanne Debik</t>
+          <t>Diana Stafsnes Califano</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5.20,67</t>
+          <t>5.19,87</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>12.02.2022</t>
+          <t>19.10.2019</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -12438,25 +12648,25 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Eirill Straum</t>
+          <t>Erle Kullerud Ytrehus</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5.21,29</t>
+          <t>5.18,84</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>10.02.2017</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -12473,25 +12683,25 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Mari Helen Hammer</t>
+          <t>Isabella Johanne Debik</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5.22,22</t>
+          <t>5.20,67</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>14.01.2005</t>
+          <t>12.02.2022</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -12508,25 +12718,25 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Embla Mimi Baarholm</t>
+          <t>Eirill Straum</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5.22,92</t>
+          <t>5.21,29</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>29.09.2018</t>
+          <t>10.02.2017</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -12543,25 +12753,25 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Synnøve Fevang</t>
+          <t>Anita Klungervik</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5.23,12</t>
+          <t>5.19,73</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>20.05.2006</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -12578,25 +12788,25 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Nina Alicja Skarø</t>
+          <t>Helle Johnsen Selsås</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5.23,58</t>
+          <t>5.20,74</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>30.09.2017</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -12613,20 +12823,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Ingrid Vie</t>
+          <t>Mari Helen Hammer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5.23,47</t>
+          <t>5.22,22</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>28.03.2025</t>
+          <t>14.01.2005</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -12648,25 +12858,25 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Emma Lu Tjeldvoll</t>
+          <t>Embla Mimi Baarholm</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5.24,60</t>
+          <t>5.22,92</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>17.03.2023</t>
+          <t>29.09.2018</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -12683,25 +12893,25 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Erle Kullerud Ytrehus</t>
+          <t>Synnøve Fevang</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5.24,74</t>
+          <t>5.23,12</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>20.05.2006</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -12718,25 +12928,25 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Emre Vold Kirkvold</t>
+          <t>Ingrid Vie</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>4.58,88</t>
+          <t>5.23,47</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>30.11.2024</t>
+          <t>28.03.2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -12753,25 +12963,25 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Hedda Grimstad-Johannessen</t>
+          <t>Nina Alicja Skarø</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5.26,00</t>
+          <t>5.23,58</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>17.01.2020</t>
+          <t>30.09.2017</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -12788,25 +12998,25 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Anita Klungervik</t>
+          <t>Emre Vold Kirkvold</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5.26,08</t>
+          <t>4.57,40</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>15.03.2024</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -12823,25 +13033,25 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Alexandra Contreras Jimenez</t>
+          <t>Michaela Josefin Abeleva Barrera</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5.26,65</t>
+          <t>5.23,02</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -12858,25 +13068,25 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Helene Marie Haram</t>
+          <t>Emma Lu Tjeldvoll</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5.26,71</t>
+          <t>5.24,60</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>25.10.2020</t>
+          <t>17.03.2023</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -12893,20 +13103,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Ane Viken Refseth</t>
+          <t>Hedda Grimstad-Johannessen</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5.28,15</t>
+          <t>5.26,00</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>13.09.2015</t>
+          <t>17.01.2020</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -12928,25 +13138,25 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Frida Pauline Busch</t>
+          <t>Helene Marie Haram</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5.28,25</t>
+          <t>5.26,71</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>20.06.2021</t>
+          <t>25.10.2020</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -12963,25 +13173,25 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Anna Svendsen</t>
+          <t>Ane Viken Refseth</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5.29,87</t>
+          <t>5.28,15</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>15.03.2019</t>
+          <t>13.09.2015</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -12998,20 +13208,20 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cecilie Solberg Jørgensen</t>
+          <t>Frida Pauline Busch</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5.30,16</t>
+          <t>5.28,25</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>29.03.2025</t>
+          <t>20.06.2021</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -13033,25 +13243,25 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Kine Marie Sørensen</t>
+          <t>Anna Svendsen</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5.30,67</t>
+          <t>5.29,87</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>08.10.2005</t>
+          <t>15.03.2019</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -13068,25 +13278,25 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Susanne Kolloen</t>
+          <t>Cecilie Solberg Jørgensen</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5.30,67</t>
+          <t>5.30,16</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>03.09.2021</t>
+          <t>29.03.2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -13103,20 +13313,20 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Kirsti Bjørnsdatter Paulsen</t>
+          <t>Kine Marie Sørensen</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5.31,36</t>
+          <t>5.30,67</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>09.02.2018</t>
+          <t>08.10.2005</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -13138,20 +13348,20 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Maria Bøe</t>
+          <t>Susanne Kolloen</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5.33,45</t>
+          <t>5.30,67</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>12.02.2010</t>
+          <t>03.09.2021</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -13173,25 +13383,25 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Hedda Fosseng Traa</t>
+          <t>Kirsti Bjørnsdatter Paulsen</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5.35,45</t>
+          <t>5.31,36</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>05.02.2016</t>
+          <t>09.02.2018</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -13208,20 +13418,20 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Silje Dahle</t>
+          <t>Kristina Aleman Sandsund</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5.35,85</t>
+          <t>5.30,58</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>19.01.2018</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -13243,25 +13453,25 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ingrid Johansen</t>
+          <t>Maria Bøe</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5.36,06</t>
+          <t>5.33,45</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>12.01.2007</t>
+          <t>12.02.2010</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -13278,25 +13488,25 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Dorottya Csejtey</t>
+          <t>Hedda Fosseng Traa</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5.38,40</t>
+          <t>5.35,45</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>10.02.2017</t>
+          <t>05.02.2016</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -13313,25 +13523,25 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Helle Johnsen Selsås</t>
+          <t>Ingrid Johansen</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5.40,43</t>
+          <t>5.36,06</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>12.01.2007</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -13348,20 +13558,20 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Ola vatn Gundersen</t>
+          <t>Silje Dahle</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5.13,33</t>
+          <t>5.35,85</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>18.01.2019</t>
+          <t>19.01.2018</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -13383,25 +13593,25 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Julie Wiik Arnesen</t>
+          <t>Nicole Kulagina</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5.42,77</t>
+          <t>5.35,17</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>25.10.2020</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -13418,25 +13628,25 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Olivia Sterud Prytz</t>
+          <t>Dorottya Csejtey</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5.43,01</t>
+          <t>5.38,40</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>30.11.2019</t>
+          <t>10.02.2017</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -13453,20 +13663,20 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Radana Konarikova</t>
+          <t>Ola vatn Gundersen</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5.43,67</t>
+          <t>5.13,33</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>03.11.2012</t>
+          <t>18.01.2019</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -13488,25 +13698,25 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sofie Hoff</t>
+          <t>Alisa Kulagina</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5.43,91</t>
+          <t>5.40,40</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -13523,25 +13733,25 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Hansine Rindberg Monsø</t>
+          <t>Guro Rønningen Osmoen</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5.44,00</t>
+          <t>5.40,81</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>30.11.2024</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -13558,25 +13768,25 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Nicole Kulagina</t>
+          <t>Julie Wiik Arnesen</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5.44,78</t>
+          <t>5.42,77</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>25.10.2020</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -13593,20 +13803,20 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Hanne Søyseth</t>
+          <t>Olivia Sterud Prytz</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5.46,50</t>
+          <t>5.43,01</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>05.02.2016</t>
+          <t>30.11.2019</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -13628,25 +13838,25 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Aurora Moen Wannebo</t>
+          <t>Radana Konarikova</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5.46,83</t>
+          <t>5.43,67</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>07.02.2014</t>
+          <t>03.11.2012</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -13663,16 +13873,16 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sofie Hepsø</t>
+          <t>Sofie Hoff</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5.47,32</t>
+          <t>5.43,91</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13698,25 +13908,25 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Aurora Alexandra Bjordal</t>
+          <t>Hansine Rindberg Monsø</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5.47,59</t>
+          <t>5.44,00</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>03.09.2021</t>
+          <t>30.11.2024</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -13733,20 +13943,20 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Guro Rønningen Osmoen</t>
+          <t>Hanne Søyseth</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5.48,29</t>
+          <t>5.46,50</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>15.03.2024</t>
+          <t>05.02.2016</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -13768,25 +13978,25 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Elise Øystrøm Tyvold</t>
+          <t>Elsa Dragsten Wake</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5.49,43</t>
+          <t>5.45,15</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>29.09.2019</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -13803,20 +14013,20 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sara Skaalvik Trelstad</t>
+          <t>Aurora Moen Wannebo</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5.51,14</t>
+          <t>5.46,83</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>08.02.2014</t>
+          <t>07.02.2014</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -13838,16 +14048,16 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Alisa Kulagina</t>
+          <t>Sofie Hepsø</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5.51,43</t>
+          <t>5.47,32</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13873,25 +14083,25 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Michaela Josefin Abeleva Barrera</t>
+          <t>Aurora Alexandra Bjordal</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5.51,85</t>
+          <t>5.47,59</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>03.09.2021</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -13908,25 +14118,25 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Oline Skjønberg</t>
+          <t>Elise Øystrøm Tyvold</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5.53,17</t>
+          <t>5.49,43</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>30.11.2019</t>
+          <t>29.09.2019</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -13943,25 +14153,25 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Marte Hemmer</t>
+          <t>Sara Skaalvik Trelstad</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5.54,68</t>
+          <t>5.51,14</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>14.01.2005</t>
+          <t>08.02.2014</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -13978,25 +14188,25 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Chloe Branlat</t>
+          <t>Oline Skjønberg</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5.56,09</t>
+          <t>5.53,17</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>30.11.2019</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -14013,25 +14223,25 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Othelie Annette Høie</t>
+          <t>Marte Hemmer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5.56,62</t>
+          <t>5.54,68</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>25.10.2014</t>
+          <t>14.01.2005</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -14048,25 +14258,25 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Selma Strandjord Lillerødvann</t>
+          <t>Chloe Branlat</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5.57,43</t>
+          <t>5.56,09</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>15.03.2024</t>
+          <t>14.03.2025</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -14083,25 +14293,25 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Aase Bjørnsdatter Paulsen</t>
+          <t>Ina Birgitte Eidsmo Hova</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5.59,96</t>
+          <t>5.54,76</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>07.02.2014</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -14118,25 +14328,25 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Arne Martin Einarsrud Rismoen</t>
+          <t>Othelie Annette Høie</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5.32,07</t>
+          <t>5.56,62</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>25.10.2014</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -14153,25 +14363,25 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Magne Petersen</t>
+          <t>Selma Strandjord Lillerødvann</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5.32,54</t>
+          <t>5.57,43</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>15.09.2013</t>
+          <t>15.03.2024</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -14188,20 +14398,20 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Ida Fiskaa Barstad</t>
+          <t>Aase Bjørnsdatter Paulsen</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>6.02,15</t>
+          <t>5.59,96</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>25.10.2020</t>
+          <t>07.02.2014</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -14223,25 +14433,25 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Izabele Farias Ribeiro</t>
+          <t>Arne Martin Einarsrud Rismoen</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>6.03,37</t>
+          <t>5.32,07</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>06.02.2015</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -14258,20 +14468,20 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Helle Lundgren</t>
+          <t>Magne Petersen</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>6.04,02</t>
+          <t>5.32,54</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>18.03.2023</t>
+          <t>15.09.2013</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -14293,25 +14503,25 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ina Birgitte Eidsmo Hova</t>
+          <t>Ida Fiskaa Barstad</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>6.05,53</t>
+          <t>6.02,15</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>17.01.2025</t>
+          <t>25.10.2020</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -14328,20 +14538,20 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Elsa Dragsten Wake</t>
+          <t>Izabele Farias Ribeiro</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>6.09,00</t>
+          <t>6.03,37</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>06.02.2015</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -14363,25 +14573,25 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sofia Bjørklund Mora</t>
+          <t>Helle Lundgren</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>6.08,93</t>
+          <t>6.04,02</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>21.03.2015</t>
+          <t>18.03.2023</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -14398,25 +14608,25 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Hege Noreng</t>
+          <t>Sofia Bjørklund Mora</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>6.12,52</t>
+          <t>6.08,93</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>08.04.2016</t>
+          <t>21.03.2015</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -14433,25 +14643,25 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Anahita Koushan</t>
+          <t>Hege Noreng</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>6.14,16</t>
+          <t>6.12,52</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>30.11.2019</t>
+          <t>08.04.2016</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -14468,25 +14678,25 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Hilde Stene Rygh</t>
+          <t>Anahita Koushan</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>6.15,83</t>
+          <t>6.14,16</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>09.03.2019</t>
+          <t>30.11.2019</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -14503,25 +14713,25 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Pia Helena Wildhagen</t>
+          <t>Hilde Stene Rygh</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>6.18,94</t>
+          <t>6.15,83</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>19.01.2018</t>
+          <t>09.03.2019</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -14538,25 +14748,25 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Ingrid Lianes</t>
+          <t>Pia Helena Wildhagen</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>6.19,72</t>
+          <t>6.18,94</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>22.05.2009</t>
+          <t>19.01.2018</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -14573,25 +14783,25 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sigrid Moen Henriksen</t>
+          <t>Ingrid Lianes</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>6.22,34</t>
+          <t>6.19,72</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>17.03.2023</t>
+          <t>22.05.2009</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -14608,25 +14818,25 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Amalie Solvoll</t>
+          <t>Sigrid Moen Henriksen</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>6.33,48</t>
+          <t>6.22,34</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>15.03.2019</t>
+          <t>17.03.2023</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -14643,25 +14853,25 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Madeleine Tran Wæraas</t>
+          <t>Marie Wærnes Blom</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>6.37,17</t>
+          <t>6.21,01</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>27.10.2019</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -14678,20 +14888,20 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Ingrid Skye Naustvoll</t>
+          <t>Elina Arefjord Spangelo</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>6.38,09</t>
+          <t>6.24,31</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>21.06.2014</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -14713,25 +14923,25 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Cathrine Hegle</t>
+          <t>Amalie Solvoll</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>6.40,05</t>
+          <t>6.33,48</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>15.05.2010</t>
+          <t>15.03.2019</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -14748,25 +14958,25 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Aurora S. Juel</t>
+          <t>Madeleine Tran Wæraas</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>6.44,06</t>
+          <t>6.37,17</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>16.06.2012</t>
+          <t>27.10.2019</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -14783,20 +14993,20 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Amalie Gylseth Dahl</t>
+          <t>Ingrid Skye Naustvoll</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>6.47,43</t>
+          <t>6.38,09</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>21.06.2014</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -14818,25 +15028,25 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Emma Nedeea Hagen</t>
+          <t>Cathrine Hegle</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>6.48,65</t>
+          <t>6.40,05</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>14.11.2021</t>
+          <t>15.05.2010</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -14853,25 +15063,25 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Emilie Sandvik Gangåssæter</t>
+          <t>Ilaria Kari Cherubini</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>6.49,16</t>
+          <t>6.41,01</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>29.09.2019</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -14888,25 +15098,25 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Julia Tan</t>
+          <t>Aurora S. Juel</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>6.49,58</t>
+          <t>6.44,06</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>18.04.2009</t>
+          <t>16.06.2012</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -14923,25 +15133,25 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Marie Wærnes Blom</t>
+          <t>Amalie Gylseth Dahl</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>6.52,92</t>
+          <t>6.47,43</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -14958,25 +15168,25 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Louise Thys</t>
+          <t>Hedda Gätzschmann</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>6.59,17</t>
+          <t>6.46,48</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -14993,20 +15203,20 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Ronja Emilia Wikström</t>
+          <t>Emma Nedeea Hagen</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>6.59,09</t>
+          <t>6.48,65</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>16.09.2023</t>
+          <t>14.11.2021</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -15028,25 +15238,25 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Camila Dorao</t>
+          <t>Emilie Sandvik Gangåssæter</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>7.00,70</t>
+          <t>6.49,16</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>16.09.2023</t>
+          <t>29.09.2019</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -15063,20 +15273,20 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Lea almaas</t>
+          <t>Julia Tan</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>7.04,43</t>
+          <t>6.49,58</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>10.02.2012</t>
+          <t>18.04.2009</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -15098,25 +15308,25 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Mia Bretun Finserå</t>
+          <t>Louise Thys</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>7.11,96</t>
+          <t>6.53,29</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>27.10.2012</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -15133,25 +15343,25 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Anna Fenstad Høysæter</t>
+          <t>Nicoline Vinje</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>7.14,33</t>
+          <t>6.54,10</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>17.01.2020</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -15168,20 +15378,20 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Amelia Roaldseth</t>
+          <t>Ronja Emilia Wikström</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>7.21,97</t>
+          <t>6.59,09</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>21.09.2008</t>
+          <t>16.09.2023</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -15203,20 +15413,20 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Ramona Vutudal</t>
+          <t>Camila Dorao</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>7.24,27</t>
+          <t>7.00,70</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>24.01.2009</t>
+          <t>16.09.2023</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -15238,25 +15448,25 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Elina Arefjord Spangelo</t>
+          <t>Lea almaas</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>7.24,00</t>
+          <t>7.04,43</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>08.12.2024</t>
+          <t>10.02.2012</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -15273,25 +15483,25 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Julia Beatrice Ferreira Kristiansen</t>
+          <t>Sigrid Gylseth Dahl</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>7.24,53</t>
+          <t>7.06,04</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>03.12.2016</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -15308,25 +15518,25 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Tora Tveiten</t>
+          <t>Mia Bretun Finserå</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>7.31,38</t>
+          <t>7.11,96</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>29.11.2014</t>
+          <t>27.10.2012</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -15343,25 +15553,25 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Aurora Dahl Bere</t>
+          <t>Anna Fenstad Høysæter</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>7.36,70</t>
+          <t>7.14,33</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>06.04.2024</t>
+          <t>17.01.2020</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -15378,20 +15588,20 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Nicoline Vinje</t>
+          <t>Charlotte Talseth</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>7.37,72</t>
+          <t>7.16,69</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>08.12.2024</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -15413,20 +15623,20 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Kristina Bragadottir</t>
+          <t>Live Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>7.42,35</t>
+          <t>7.19,20</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>16.06.2012</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -15448,25 +15658,25 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Live Hamnes Ulriksen</t>
+          <t>Amelia Roaldseth</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>7.45,53</t>
+          <t>7.21,97</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>30.11.2024</t>
+          <t>21.09.2008</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -15483,25 +15693,25 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Connie Rakel Lånke</t>
+          <t>Ramona Vutudal</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>7.57,66</t>
+          <t>7.24,27</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>05.04.2014</t>
+          <t>24.01.2009</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -15518,20 +15728,20 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Ilaria Kari Cherubini</t>
+          <t>Julia Beatrice Ferreira Kristiansen</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>7.59,17</t>
+          <t>7.24,53</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>22.02.2025</t>
+          <t>03.12.2016</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -15553,25 +15763,25 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Charlotte Talseth</t>
+          <t>Tora Tveiten</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>8.06,12</t>
+          <t>7.31,38</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>08.12.2024</t>
+          <t>29.11.2014</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -15588,20 +15798,20 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Sigrid Gylseth Dahl</t>
+          <t>Aurora Dahl Bere</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>8.09,26</t>
+          <t>7.36,70</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>30.11.2024</t>
+          <t>06.04.2024</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -15623,20 +15833,20 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Sunniva Eldholm</t>
+          <t>Oda Brennhaug Tangen</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>8.14,05</t>
+          <t>7.37,28</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>17.04.2021</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -15658,20 +15868,20 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Aida Smalø Moen</t>
+          <t>Kristina Bragadottir</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>8.16,82</t>
+          <t>7.42,35</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>18.09.2011</t>
+          <t>16.06.2012</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -15698,20 +15908,20 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>8.24,90</t>
+          <t>7.45,16</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>08.12.2024</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -15728,25 +15938,25 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Frida Merethe Norli Eidsvåg</t>
+          <t>Connie Rakel Lånke</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>8.25,93</t>
+          <t>7.57,66</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>21.06.2014</t>
+          <t>05.04.2014</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -15763,20 +15973,20 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Eline Nergård Wilhelmsen</t>
+          <t>Sunniva Eldholm</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>8.31,66</t>
+          <t>8.14,05</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>08.12.2024</t>
+          <t>17.04.2021</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -15798,20 +16008,20 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Jassmitha Ajeethsing</t>
+          <t>Emilie Magnussen</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>8.33,33</t>
+          <t>8.15,78</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>17.01.2020</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -15833,25 +16043,25 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Camilla Gervasoni</t>
+          <t>Aida Smalø Moen</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>8.40,05</t>
+          <t>8.16,82</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>03.12.2011</t>
+          <t>18.09.2011</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -15868,25 +16078,25 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Aida Sofie Feyzi</t>
+          <t>Frida Merethe Norli Eidsvåg</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>8.44,42</t>
+          <t>8.25,93</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>29.09.2018</t>
+          <t>21.06.2014</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -15903,20 +16113,20 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Aurora Marken Fredriksen</t>
+          <t>Eline Nergård Wilhelmsen</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>8.55,96</t>
+          <t>8.31,66</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>17.04.2021</t>
+          <t>08.12.2024</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -15938,20 +16148,20 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Elena Fyhn Leida</t>
+          <t>Vilma Granhus Følstad</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>9.05,38</t>
+          <t>8.31,76</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>20.06.2021</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -15973,25 +16183,25 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Phoebe Thalberg Fagerheim</t>
+          <t>Jassmitha Ajeethsing</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>9.30,95</t>
+          <t>8.33,33</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>24.11.2012</t>
+          <t>17.01.2020</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -16008,33 +16218,243 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
+          <t>Camilla Gervasoni</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>8.40,05</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>87</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>03.12.2011</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Stjørdal</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Aida Sofie Feyzi</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>8.44,42</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>85</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>29.09.2018</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Husebybadet</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Aurora Marken Fredriksen</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>8.55,96</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>80</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>17.04.2021</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Elena Fyhn Leida</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>9.05,38</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>76</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>20.06.2021</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Shiva Sattanathan</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>8.22,60</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>75</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>29.11.2025</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Stjørdal</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Phoebe Thalberg Fagerheim</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>9.30,95</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>66</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>24.11.2012</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Stjørdal</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
           <t>Kristine Haram Bye</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B181" t="inlineStr">
         <is>
           <t>10.49,84</t>
         </is>
       </c>
-      <c r="C175" t="n">
+      <c r="C181" t="n">
         <v>45</v>
       </c>
-      <c r="D175" t="inlineStr">
+      <c r="D181" t="inlineStr">
         <is>
           <t>30.10.2010</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Trondheim</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
@@ -17074,12 +17494,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Silje Aadahl</t>
+          <t>Ada Fludal Osland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5.22,12</t>
+          <t>5.22,13</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -17087,12 +17507,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>09.07.2017</t>
+          <t>27.06.2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -17109,12 +17529,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ada Fludal Osland</t>
+          <t>Silje Aadahl</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5.22,13</t>
+          <t>5.22,12</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -17122,12 +17542,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>27.06.2025</t>
+          <t>09.07.2017</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -17389,12 +17809,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Kirsti Bjørnsdatter Paulsen</t>
+          <t>Erika Nicole Hagen</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5.29,69</t>
+          <t>5.29,96</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -17402,7 +17822,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10.06.2018</t>
+          <t>01.05.2022</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -17424,12 +17844,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Erika Nicole Hagen</t>
+          <t>Kirsti Bjørnsdatter Paulsen</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5.29,96</t>
+          <t>5.29,69</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -17437,7 +17857,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>01.05.2022</t>
+          <t>10.06.2018</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18159,12 +18579,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Elise Øystrøm Tyvold</t>
+          <t>Elsa Dragsten Wake</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>6.06,32</t>
+          <t>6.06,17</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -18172,7 +18592,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>16.06.2019</t>
+          <t>15.06.2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -18194,12 +18614,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Elsa Dragsten Wake</t>
+          <t>Elise Øystrøm Tyvold</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>6.06,17</t>
+          <t>6.06,32</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -18207,7 +18627,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>15.06.2025</t>
+          <t>16.06.2019</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
